--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Clase-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,0</t>
+          <t>1,69; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,58</t>
+          <t>-1,05; 4,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,83</t>
+          <t>2,47; 7,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,52; 263,98</t>
+          <t>-38,29; 265,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,48; 284,17</t>
+          <t>47,82; 288,16</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 5,64</t>
+          <t>0,02; 5,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,01</t>
+          <t>-0,38; 4,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,92</t>
+          <t>3,88; 10,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 560,9</t>
+          <t>-13,16; 487,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 578,11</t>
+          <t>-36,37; 922,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,96; 295,47</t>
+          <t>63,29; 311,3</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 5,55</t>
+          <t>-1,45; 5,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 19,05</t>
+          <t>6,49; 19,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 19,91</t>
+          <t>7,15; 20,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 156,06</t>
+          <t>-26,99; 164,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>179,4; 1058,22</t>
+          <t>189,2; 1107,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,03; 853,9</t>
+          <t>74,34; 802,47</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,58</t>
+          <t>-1,74; 2,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,87</t>
+          <t>0,85; 4,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 2,26</t>
+          <t>-5,96; 2,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,54; 54,44</t>
+          <t>-27,73; 61,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,59; 173,46</t>
+          <t>18,27; 179,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,09; 24,71</t>
+          <t>-54,19; 22,78</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,04</t>
+          <t>6,11; 12,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,43</t>
+          <t>3,6; 9,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 16,17</t>
+          <t>7,01; 16,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122,6; 519,97</t>
+          <t>119,53; 500,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,15; 223,84</t>
+          <t>51,28; 219,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,63; 210,72</t>
+          <t>68,33; 228,41</t>
         </is>
       </c>
     </row>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,14; 14,7</t>
+          <t>9,77; 14,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,95; 13,32</t>
+          <t>8,97; 13,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,22; 18,3</t>
+          <t>13,15; 18,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>420,62; —</t>
+          <t>419,88; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>414,64; 3149,48</t>
+          <t>398,11; 2549,01</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,9</t>
+          <t>4,42; 6,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,89</t>
+          <t>4,67; 7,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,45</t>
+          <t>4,86; 9,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110,46; 223,4</t>
+          <t>109,3; 221,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>129,3; 256,07</t>
+          <t>130,49; 264,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,18; 174,59</t>
+          <t>73,18; 174,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Clase-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>4,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>134,66%</t>
+          <t>124,43%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,04</t>
+          <t>1,65; 6,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,77</t>
+          <t>-1,2; 4,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,7</t>
+          <t>2,51; 7,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 265,95</t>
+          <t>-35,59; 261,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,82; 288,16</t>
+          <t>45,2; 267,14</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>6,92</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>152,22%</t>
+          <t>158,28%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,46</t>
+          <t>-0,17; 5,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,34</t>
+          <t>-0,59; 4,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,05</t>
+          <t>4,18; 10,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 487,78</t>
+          <t>-15,51; 465,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,37; 922,51</t>
+          <t>-45,72; 740,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,29; 311,3</t>
+          <t>70,05; 324,09</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,36</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>211,27%</t>
+          <t>102,67%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,41</t>
+          <t>-1,51; 5,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 19,12</t>
+          <t>6,75; 18,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 20,43</t>
+          <t>3,98; 14,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 164,84</t>
+          <t>-30,53; 160,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>189,2; 1107,04</t>
+          <t>174,95; 1027,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,34; 802,47</t>
+          <t>37,64; 191,65</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,04%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,88</t>
+          <t>-1,75; 2,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,97</t>
+          <t>1,01; 4,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 2,12</t>
+          <t>-0,78; 3,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 61,22</t>
+          <t>-27,56; 58,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,27; 179,97</t>
+          <t>25,83; 173,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,19; 22,78</t>
+          <t>-7,33; 46,59</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,03</t>
+          <t>14,79</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>130,86%</t>
+          <t>182,52%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 12,32</t>
+          <t>6,41; 12,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,55</t>
+          <t>3,67; 9,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 16,79</t>
+          <t>11,74; 17,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119,53; 500,27</t>
+          <t>122,4; 505,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,28; 219,91</t>
+          <t>51,48; 214,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,33; 228,41</t>
+          <t>113,18; 269,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,69</t>
+          <t>15,23</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1017,28%</t>
+          <t>969,79%</t>
         </is>
       </c>
     </row>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,61</t>
+          <t>10,15; 14,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,36</t>
+          <t>8,95; 13,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,15; 18,04</t>
+          <t>12,68; 17,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>419,88; —</t>
+          <t>423,03; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>398,11; 2549,01</t>
+          <t>356,79; 2749,5</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>111,74%</t>
+          <t>116,85%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,86</t>
+          <t>4,57; 6,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,11</t>
+          <t>4,55; 6,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 9,42</t>
+          <t>6,92; 9,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109,3; 221,31</t>
+          <t>110,39; 219,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>130,49; 264,05</t>
+          <t>128,67; 252,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,18; 174,79</t>
+          <t>91,12; 147,82</t>
         </is>
       </c>
     </row>
